--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medication.xlsx
@@ -371,7 +371,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
